--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1367B04-F6F2-42DE-87F6-F34A85F68192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5688E6-CAAA-4492-844F-AB4C102DC856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1194,7 +1194,10 @@
       <c r="D3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="13">
+        <f xml:space="preserve"> SUM(B3+A3)</f>
+        <v>24</v>
+      </c>
       <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.3">
@@ -1210,7 +1213,10 @@
       <c r="D4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="13">
+        <f>SUMIF(C3:C12,C3,B3:B12)</f>
+        <v>48</v>
+      </c>
       <c r="F4" s="14"/>
       <c r="L4" s="2" t="s">
         <v>25</v>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5688E6-CAAA-4492-844F-AB4C102DC856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08A4AA6-11EC-4900-8ACB-52B40179CF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1240,7 +1240,10 @@
       <c r="D5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="13">
+        <f>SUMIFS(B3:B12,C3:C12,C3,D3:D12,D3)</f>
+        <v>23</v>
+      </c>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08A4AA6-11EC-4900-8ACB-52B40179CF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965B7F88-DFA2-4E1F-A8F8-13BC04E38ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1261,7 +1261,10 @@
       <c r="D6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="13">
+        <f>MIN(B3:B12)</f>
+        <v>23</v>
+      </c>
       <c r="L6" s="2" t="s">
         <v>34</v>
       </c>
@@ -1284,7 +1287,10 @@
       <c r="D7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="13"/>
+      <c r="E7" s="13">
+        <f>MAX(B3:B12)</f>
+        <v>31</v>
+      </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1302,7 +1308,10 @@
       <c r="D8" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="13">
+        <f>AVERAGE(B3:B12)</f>
+        <v>26.7</v>
+      </c>
       <c r="H8" s="19" t="s">
         <v>39</v>
       </c>
@@ -1328,7 +1337,10 @@
       <c r="D9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="13"/>
+      <c r="E9" s="13">
+        <f>PRODUCT(B3,A3)</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="1:15" ht="21" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
@@ -1343,7 +1355,10 @@
       <c r="D10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="13">
+        <f>QUOTIENT(A8,A4)</f>
+        <v>3</v>
+      </c>
       <c r="H10" s="13" t="s">
         <v>46</v>
       </c>
@@ -1361,7 +1376,10 @@
       <c r="D11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="13"/>
+      <c r="E11" s="13">
+        <f>MOD(A8,A4)</f>
+        <v>0</v>
+      </c>
       <c r="H11" s="13" t="s">
         <v>48</v>
       </c>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965B7F88-DFA2-4E1F-A8F8-13BC04E38ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ECD77F-4FB9-43EF-910E-6B8BA9CD6922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1397,7 +1397,10 @@
       <c r="D12" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="13">
+        <f>POWER(A12,A4)</f>
+        <v>100</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="21" x14ac:dyDescent="0.3">
       <c r="A25" s="11">

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68ECD77F-4FB9-43EF-910E-6B8BA9CD6922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1081954E-8982-410E-8695-D0F19D959BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arithmetic and statistical" sheetId="1" r:id="rId1"/>
@@ -1415,7 +1415,10 @@
       <c r="D25" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="13"/>
+      <c r="E25" s="13">
+        <f>_xlfn.VAR.S(B25:B28)</f>
+        <v>36000000</v>
+      </c>
       <c r="G25" s="5" t="s">
         <v>51</v>
       </c>
@@ -1439,7 +1442,10 @@
       <c r="D26" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="13"/>
+      <c r="E26" s="13">
+        <f>_xlfn.VAR.P(B25:B28)</f>
+        <v>27000000</v>
+      </c>
     </row>
     <row r="27" spans="1:14" ht="21" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
@@ -1454,7 +1460,10 @@
       <c r="D27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="13"/>
+      <c r="E27" s="13">
+        <f>_xlfn.STDEV.S(B25:B28)</f>
+        <v>6000</v>
+      </c>
       <c r="G27" s="5" t="s">
         <v>55</v>
       </c>
@@ -1473,7 +1482,10 @@
       <c r="D28" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="13"/>
+      <c r="E28" s="13">
+        <f>_xlfn.STDEV.P(B25:B28)</f>
+        <v>5196.152422706632</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="J30" s="3" t="s">
@@ -1508,7 +1520,10 @@
       <c r="D35" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="E35" s="13"/>
+      <c r="E35" s="13">
+        <f>MAX(B35:B37) - MIN(A35:A37)</f>
+        <v>23</v>
+      </c>
       <c r="G35" s="23" t="s">
         <v>61</v>
       </c>
@@ -1520,7 +1535,7 @@
         <v>16</v>
       </c>
       <c r="B36" s="11">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>42</v>
@@ -1528,7 +1543,10 @@
       <c r="D36" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E36" s="13"/>
+      <c r="E36" s="13">
+        <f>MEDIAN(B35:B37)</f>
+        <v>36</v>
+      </c>
       <c r="G36" s="23" t="s">
         <v>63</v>
       </c>
@@ -1548,7 +1566,10 @@
       <c r="D37" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="13"/>
+      <c r="E37" s="13">
+        <f>MODE(B35:B37)</f>
+        <v>36</v>
+      </c>
       <c r="G37" s="23" t="s">
         <v>65</v>
       </c>
@@ -2534,8 +2555,8 @@
   <dimension ref="A1:E1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>

--- a/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
+++ b/11_Demos_and_Workbooks/03_Formulas_and_Functions/Formulas_&_Functions_Part_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\courses\Data Analysis 26-27\7-Introducation to Data Fields (Excel)\11_Demos_and_Workbooks\03_Formulas_and_Functions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1081954E-8982-410E-8695-D0F19D959BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F2E1AB-4B94-4DF5-8865-88675B728882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arithmetic and statistical" sheetId="1" r:id="rId1"/>
@@ -2592,7 +2592,10 @@
       <c r="D3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="13">
+        <f>COUNT(B3:B7)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A4" s="11">
@@ -2607,7 +2610,10 @@
       <c r="D4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="13">
+        <f>COUNTA(B3:B7)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
@@ -2622,7 +2628,10 @@
       <c r="D5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="13">
+        <f>COUNTBLANK(B3:B7)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
@@ -2637,7 +2646,10 @@
       <c r="D6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="13">
+        <f>COUNTIF(C3:C7,C3)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="21" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
@@ -2650,7 +2662,10 @@
       <c r="D7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="13"/>
+      <c r="E7" s="13">
+        <f>COUNTIFS(B3:B7,C3,A3:A7,C3)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3661,7 +3676,7 @@
   <cols>
     <col min="1" max="1" width="13.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="43.44140625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="5.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.21875" style="15" customWidth="1"/>
     <col min="4" max="4" width="5" style="15" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.88671875" style="15" bestFit="1" customWidth="1"/>
     <col min="6" max="26" width="8.6640625" style="15" customWidth="1"/>
@@ -3686,43 +3701,64 @@
       <c r="B5" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="28"/>
+      <c r="C5" s="28" t="str">
+        <f>_xlfn.CONCAT(C1:D1)</f>
+        <v xml:space="preserve">Cairo </v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="28"/>
+      <c r="C6" s="28" t="str">
+        <f>LEFT(A1,3)</f>
+        <v>Mos</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B7" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="28"/>
+      <c r="C7" s="28" t="str">
+        <f>RIGHT(A1,4)</f>
+        <v xml:space="preserve">afa </v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B8" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="28"/>
+      <c r="C8" s="28" t="str">
+        <f>MID(A1,3,3)</f>
+        <v>sta</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="28"/>
+      <c r="C9" s="28">
+        <f>LEN(A1)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B10" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="28" t="str">
+        <f>TRIM(B1)</f>
+        <v>MAN United</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B11" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="28" t="str">
+        <f>SUBSTITUTE(B1,B1,C10)</f>
+        <v>MAN United</v>
+      </c>
       <c r="E11" s="29" t="s">
         <v>15</v>
       </c>
@@ -3737,25 +3773,37 @@
       <c r="B12" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="28">
+        <f>FIND("MAN", B1)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="28" t="str">
+        <f>UPPER(E11)</f>
+        <v>INSTANCE</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B14" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="28" t="str">
+        <f>LOWER(C10)</f>
+        <v>man united</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="18" x14ac:dyDescent="0.3">
       <c r="B15" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="28" t="str">
+        <f>PROPER(C13)</f>
+        <v>Instance</v>
+      </c>
     </row>
     <row r="17" s="15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="18" s="15" customFormat="1" x14ac:dyDescent="0.3"/>
